--- a/basedatos_partidas/salida/descompuestos/CT-11-01-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-11-01-020.xlsx
@@ -539,10 +539,10 @@
         <v>0.042</v>
       </c>
       <c r="G10" t="n">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>13.44</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="11">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>30.47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>42.18</v>
+        <v>40.71</v>
       </c>
       <c r="H25" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>42.6</v>
+        <v>41.12</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-11-01-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-11-01-020.xlsx
@@ -617,10 +617,10 @@
         <v>0.45</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="15">
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>40.71</v>
+        <v>41.07</v>
       </c>
       <c r="H25" t="n">
         <v>0.41</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>41.12</v>
+        <v>41.48</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-11-01-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-11-01-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 11 Techos y cubiertas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Estructura de techo</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
